--- a/Tools/DB_Import_Template.xlsx
+++ b/Tools/DB_Import_Template.xlsx
@@ -23,13 +23,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -40,29 +58,6 @@
       <i val="1"/>
       <color rgb="00555555"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <color rgb="00333333"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -114,31 +109,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,109 +497,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DB Import Template — IndustrialAssets</t>
+          <t>DB Import Template - IndustrialAssets</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
       <c r="A2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>How to use this file:</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>1. Fill in each sheet with your own asset/datapoint/channel/file data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
+          <t>1. Fill ASSETS, DATAPOINTS, DATACHANNELS, and DATAFILES with your import data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2. Row 1 = column headers  |  Row 2 = notes/constraints  |  Row 3 onwards = your data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
+          <t>2. TOPICMAPPINGS is generated from DATACHANNELS by the DB bootstrap logic. Treat it as reference-only unless you are doing a custom migration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>3. IDs must be unique within each table and consistent across related tables (FK references).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
+          <t>3. ASSETACCESS is usually assigned by access-control policy after import. Only prefill it if you already know the exact DB users-to-assets grants you want.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>4. For TOPICMAPPINGS — leave ID as (auto); the init SQL generates it from DATACHANNELS automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
+          <t>4. Row 1 = headers, Row 2 = constraints/notes, Row 3+ = data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. For ASSETACCESS — leave ID as (auto); add one row per user+asset combination you want to allow.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>6. Once filled, generate a seed SQL script from your data or use a SQL import tool to load the rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="8" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Sheet order matches FK dependency order:</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
+          <t>5. Sheet order follows FK dependency: ASSETS -&gt; DATAPOINTS -&gt; DATACHANNELS -&gt; DATAFILES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="8" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Important behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>- DATACHANNELS.Target stores the opaque MQTT alias used by Unity/broker, such as mx/7a/01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ASSETS → DATAPOINTS → DATACHANNELS → DATAFILES → TOPICMAPPINGS → ASSETACCESS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1">
-      <c r="A13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>MQTT Target field (DATACHANNELS.Target):</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Use opaque alias paths like mx/7a/01 — these are the broker topic UIDs, not raw device paths.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Real device topic paths go in TOPICMAPPINGS.RealTopicPath.</t>
+          <t>- TOPICMAPPINGS.RealTopicPath stores the raw device topic and is derived during topic bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>- ASSETACCESS controls which DB login can see which asset.</t>
         </is>
       </c>
     </row>
@@ -627,129 +602,129 @@
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>MessagingRole</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>MessagingRoleCode</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>PK NVARCHAR(64) e.g. b101</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Display name NVARCHAR(256)</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Short description NVARCHAR(1024)</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>subscriber|publisher|both</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>0=sub 1=pub 2=both</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>0=inactive 1=active</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Test Station</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>leaktest - Performs pressure decay and leak-rate qualification.</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>subscriber</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>b102</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Pressure Sensor</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>pressure01 - Primary pressure transducer feeding leak test telemetry.</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>both</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -768,263 +743,263 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ASSET_ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>PK NVARCHAR(64)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FK → ASSETS.ID</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; ASSETS.ID</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Display name NVARCHAR(256)</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Short description NVARCHAR(1024)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>0=inactive 1=active</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Pressure Hold</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Validates pressure hold during timed window.</t>
         </is>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>c102</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Fill and Charge</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Tracks fill flow and ramp-up pressure profile.</t>
         </is>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>c103</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Temperature Compensation</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Compensates pressure against ambient/part temperature.</t>
         </is>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>c104</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Gross Leak Detection</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Immediate alarm for rapid pressure drop events.</t>
         </is>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>c105</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Fine Leak Quantification</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Computes leak rate versus acceptance limit.</t>
         </is>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>c106</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Test Verdict</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Pass/fail decision and reason code.</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>d101</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>b102</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Sensor Telemetry</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Live transducer readings and health metrics.</t>
         </is>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>d102</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>b102</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Sensor Diagnostics</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Calibration and drift indicators.</t>
         </is>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1039,686 +1014,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ASSET_ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>DATAPOINT_ID</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>PK NVARCHAR(64)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FK → ASSETS.ID</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FK → DATAPOINTS.ID</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; ASSETS.ID</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; DATAPOINTS.ID</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Display name NVARCHAR(256)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Short description NVARCHAR(1024)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>MQTT topic path e.g. mx/7a/01</t>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Opaque MQTT alias used by Unity/broker, e.g. mx/7a/01</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>e101</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Hold Pressure PSI</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Current hold pressure.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>mx/7a/01</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>e102</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Hold Timer Sec</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>Elapsed hold timer.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>mx/7a/02</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>e103</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Pressure Decay</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Pressure decay slope during hold.</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>mx/7a/03</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>e104</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>c102</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Fill Flow SCCM</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Fill flow command/actual.</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>mx/7a/04</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>e105</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>c102</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Charge Pressure PSI</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>Pressure during charge ramp.</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>mx/7a/05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>e106</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>c103</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Ambient Temp C</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Ambient temperature.</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/06</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>e107</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>c103</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Part Temp C</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Part body temperature.</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/07</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>e108</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>c103</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Comp Pressure PSI</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Temperature compensated pressure.</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>e109</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>c104</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Gross Leak Alarm</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Boolean alarm for gross leak.</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/09</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>e10a</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>c104</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>Rapid Drop Flag</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>Rapid drop detection flag.</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>e10b</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>c105</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>Leak Rate SCCM</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>Computed leak rate.</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>e10c</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>c105</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Leak Limit SCCM</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Configured leak acceptance limit.</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>e10d</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>c106</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Pass Fail</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Final pass/fail bit.</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>e10e</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>c106</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Result Code</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Failure mode / result code.</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/0e</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>e201</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>d101</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Pressure PSI</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Raw sensor pressure reading.</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/01</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>e202</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>d101</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>Pressure Filtered</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Filtered pressure value.</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>e203</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>d101</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
-        <is>
-          <t>Sensor Health</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>Health/quality indicator.</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>e204</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>d102</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>Calibration Due</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>Calibration due flag.</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/04</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>e205</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>d102</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Drift PPM</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Estimated sensor drift.</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/05</t>
         </is>
       </c>
     </row>
@@ -1733,311 +1260,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>ASSET_ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>DATAPOINT_ID</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>PK NVARCHAR(64)</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FK → ASSETS.ID</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FK → DATAPOINTS.ID</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; ASSETS.ID</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; DATAPOINTS.ID</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Display name NVARCHAR(256)</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Short description NVARCHAR(1024)</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>pdf|csv|xlsx|url|unc</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Relative path or URL NVARCHAR(1024)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>f101</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Hold Procedure</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Work instruction for pressure hold.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>pdf</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>docs/leaktest/hold_procedure.pdf</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>f102</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>c101</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Hold Trend Template</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>CSV template for hold trend export.</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>docs/leaktest/templates/hold_trend_template.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>f103</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>c105</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Leak Formula</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Leak-rate calculation worksheet.</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>xlsx</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>docs/leaktest/calcs/leak_formula.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>f104</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>c106</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Result Report</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Final pass/fail signed report.</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>docs/leaktest/reports/result_report.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>f201</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>d101</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Sensor Datasheet</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Pressure sensor technical datasheet.</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>docs/sensors/pressure01/datasheet.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>f202</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>d102</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Calibration Cert</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Latest calibration certificate.</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>docs/sensors/pressure01/calibration_cert.pdf</t>
         </is>
       </c>
     </row>
@@ -2052,121 +1431,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>CHANNEL_ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>ASSET_ID</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>TopicUID</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>RealTopicPath</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>PK NVARCHAR(64) use NEWID()</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>FK → DATACHANNELS.ID (unique)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FK → ASSETS.ID</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>Opaque alias e.g. mx/7a/01 — auto-generated by init SQL</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>Actual MQTT topic sent by the device e.g. plant/leaktest/hold/pressure_psi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>(auto)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>e101</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>b101</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>mx/7a/01</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>plant/leaktest/hold/pressure_psi</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>(auto)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>e201</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>b102</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>mx/9c/01</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>plant/pressure01/sensor/psi</t>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Generated by bootstrap logic; leave blank for normal imports</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Derived from DATACHANNELS.ID</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Derived from DATACHANNELS.ASSET_ID</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Usually same opaque alias pattern as DATACHANNELS.Target</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Raw device topic path; only used for advanced/manual migrations</t>
         </is>
       </c>
     </row>
@@ -2184,74 +1509,66 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>USER_ID</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>ASSET_ID</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>PK NVARCHAR(64) use NEWID()</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Optional/manual only; can be assigned after import</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>DB login name e.g. app_reader</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>FK → ASSETS.ID — grants this user access to this asset</t>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>FK -&gt; ASSETS.ID</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>(auto)</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>app_reader</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>b101</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>(auto)</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>app_reader</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>b102</t>
         </is>
